--- a/form.xlsx
+++ b/form.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chincon\Documents\GitHub\711barcode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9C56461A-92F2-4899-9358-730E948EECF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836D4A54-859E-4EC0-915D-5EFCD2170341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{030359CC-077D-4FBA-8811-510F823DA2A1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>分類</t>
   </si>
@@ -67,13 +67,29 @@
   </si>
   <si>
     <t>https://pcsccloud-my.sharepoint.com/:f:/g/personal/jeromelu_mail_7-11_com_tw/IgBM4yKJ7SztQ5Y22UxAH2XLAfl7zqeZ2A8V0BxeZ-avNIQ?e=wVdEr1</t>
+  </si>
+  <si>
+    <t>https://pcsccloud-my.sharepoint.com/:p:/g/personal/jeromelu_mail_7-11_com_tw/IQAzBaJexaaUR5t1MhYVDD4DAc8HaDM2uOvuCZwfi9_V8zQ?e=159Lhc</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>POP相關</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>停止/暫停營業POP</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>請修改內部文字列印使用</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -228,6 +244,15 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -531,7 +556,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -658,13 +683,19 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - 輔色1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - 輔色2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - 輔色3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -690,6 +721,7 @@
     <cellStyle name="計算方式" xfId="11" builtinId="22" customBuiltin="1"/>
     <cellStyle name="連結的儲存格" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="備註" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="超連結" xfId="42" builtinId="8"/>
     <cellStyle name="說明文字" xfId="16" builtinId="53" customBuiltin="1"/>
     <cellStyle name="輔色1" xfId="18" builtinId="29" customBuiltin="1"/>
     <cellStyle name="輔色2" xfId="22" builtinId="33" customBuiltin="1"/>
@@ -1038,7 +1070,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A66FE25F-10D3-4466-9C02-1724BF3E9F94}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.4">
@@ -1097,8 +1129,25 @@
         <v>13</v>
       </c>
     </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D5" r:id="rId1" xr:uid="{26E2842C-A257-45F5-AC2E-FD6B7ACE9E31}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>